--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>15 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2396.76</v>
+        <v>16207.97</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2396.76</v>
+        <v>16207.97</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,16 +502,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -539,16 +539,188 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2623.27</v>
       </c>
       <c r="L5" t="n">
-        <v>49020.81</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>49020.81</v>
+        <v>2623.27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>119223</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OSCAR RAMIREZ RUIZ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12054.68</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12054.68</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38468.95</v>
+      </c>
+      <c r="M6" t="n">
+        <v>38468.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>120051</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2488.17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2488.17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>27369.85</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27369.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>119447</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1742.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1742.89</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>71981.92</v>
+      </c>
+      <c r="M8" t="n">
+        <v>71981.92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>116795</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4796.14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4796.14</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>15 de septiembre de 2026</t>
+          <t>17 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>17 de septiembre de 2026</t>
+          <t>22 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>12054.68</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2401.3</v>
       </c>
       <c r="I6" t="n">
-        <v>12054.68</v>
+        <v>14455.98</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>38468.95</v>
+        <v>36067.65</v>
       </c>
       <c r="M6" t="n">
-        <v>38468.95</v>
+        <v>36067.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2488.17</v>
+        <v>1742.89</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4800.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2488.17</v>
+        <v>6543.81</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>27369.85</v>
+        <v>67181</v>
       </c>
       <c r="M7" t="n">
-        <v>27369.85</v>
+        <v>67181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -659,13 +659,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1742.89</v>
+        <v>2488.17</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1742.89</v>
+        <v>2488.17</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>71981.92</v>
+        <v>27369.85</v>
       </c>
       <c r="M8" t="n">
-        <v>71981.92</v>
+        <v>27369.85</v>
       </c>
     </row>
     <row r="9">
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1598.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1598.75</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4796.14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4796.14</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>22 de septiembre de 2026</t>
+          <t>25 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>25 de septiembre de 2026</t>
+          <t>29 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>12054.68</v>
+        <v>29059.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2401.3</v>
+        <v>4800.92</v>
       </c>
       <c r="I6" t="n">
-        <v>14455.98</v>
+        <v>33860.27</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>36067.65</v>
+        <v>67181</v>
       </c>
       <c r="M6" t="n">
-        <v>36067.65</v>
+        <v>67181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1742.89</v>
+        <v>12054.68</v>
       </c>
       <c r="H7" t="n">
-        <v>4800.92</v>
+        <v>2401.3</v>
       </c>
       <c r="I7" t="n">
-        <v>6543.81</v>
+        <v>14455.98</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>67181</v>
+        <v>36067.65</v>
       </c>
       <c r="M7" t="n">
-        <v>67181</v>
+        <v>36067.65</v>
       </c>
     </row>
     <row r="8">

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,6 +434,7 @@
       <c r="K1" t="inlineStr"/>
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -449,6 +450,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -464,6 +466,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -507,6 +510,11 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -549,6 +557,11 @@
       </c>
       <c r="M5" t="n">
         <v>2623.27</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -593,6 +606,11 @@
       <c r="M6" t="n">
         <v>67181</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,6 +654,11 @@
       <c r="M7" t="n">
         <v>36067.65</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,6 +702,11 @@
       <c r="M8" t="n">
         <v>27369.85</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -721,6 +749,11 @@
       </c>
       <c r="M9" t="n">
         <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>29 de septiembre de 2026</t>
+          <t>30 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,22 +577,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>29059.35</v>
+        <v>12086.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4800.92</v>
+        <v>2407.73</v>
       </c>
       <c r="I6" t="n">
-        <v>33860.27</v>
+        <v>14494.71</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -601,21 +601,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>67181</v>
+        <v>36164.3</v>
       </c>
       <c r="M6" t="n">
-        <v>67181</v>
+        <v>36164.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -634,13 +634,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>12054.68</v>
+        <v>2494.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2401.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14455.98</v>
+        <v>2494.84</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -649,21 +649,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>36067.65</v>
+        <v>27443.2</v>
       </c>
       <c r="M7" t="n">
-        <v>36067.65</v>
+        <v>27443.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,22 +673,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2488.17</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1603.03</v>
       </c>
       <c r="I8" t="n">
-        <v>2488.17</v>
+        <v>1603.03</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -697,60 +697,12 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>27369.85</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>27369.85</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>116795</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1598.75</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1598.75</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
         <is>
           <t>2025-12-09</t>
         </is>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>30 de septiembre de 2026</t>
+          <t>12 de octubre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -471,7 +471,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -481,38 +481,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>16207.97</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>16207.97</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2623.27</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2623.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5246.54</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -535,28 +535,28 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2623.27</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>65824.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2623.27</v>
+        <v>65824.42</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>120596</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,45 +577,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>OLGA SOFIA GAXIOLA IBARRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>12086.98</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2407.73</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14494.71</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>42182.62</v>
       </c>
       <c r="L6" t="n">
-        <v>36164.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>36164.3</v>
+        <v>42182.62</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -625,22 +625,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2494.84</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2494.84</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -649,62 +649,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>27443.2</v>
+        <v>36164.3</v>
       </c>
       <c r="M7" t="n">
-        <v>27443.2</v>
+        <v>36164.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>116795</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1603.03</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1603.03</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>12 de octubre de 2026</t>
+          <t>13 de octubre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>13 de octubre de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -595,16 +595,16 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>42182.62</v>
+        <v>74804.00999999999</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>42182.62</v>
+        <v>74804.00999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -643,16 +643,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>76268.8</v>
       </c>
       <c r="L7" t="n">
         <v>36164.3</v>
       </c>
       <c r="M7" t="n">
-        <v>36164.3</v>
+        <v>112433.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>16 de octubre de 2026</t>
+          <t>19 de octubre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -487,28 +487,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2623.27</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2623.27</v>
+        <v>65824.42</v>
       </c>
       <c r="M4" t="n">
-        <v>5246.54</v>
+        <v>65824.42</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>120704</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,38 +529,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>BRUNO PADILLA SALDATE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>3489.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3489.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>43536.36</v>
       </c>
       <c r="L5" t="n">
-        <v>65824.42</v>
+        <v>43536.36</v>
       </c>
       <c r="M5" t="n">
-        <v>65824.42</v>
+        <v>87072.72</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>19 de octubre de 2026</t>
+          <t>21 de octubre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -471,7 +471,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>120596</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -481,45 +481,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>OLGA SOFIA GAXIOLA IBARRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>3489.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3489.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6468.97</v>
       </c>
       <c r="L4" t="n">
-        <v>65824.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>65824.42</v>
+        <v>6468.97</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>120704</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,45 +529,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BRUNO PADILLA SALDATE</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>76268.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2407.73</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>78676.53</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>43536.36</v>
+        <v>1926.72</v>
       </c>
       <c r="L5" t="n">
-        <v>43536.36</v>
+        <v>54950.44</v>
       </c>
       <c r="M5" t="n">
-        <v>87072.72</v>
+        <v>56877.16</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>120596</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,45 +577,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OLGA SOFIA GAXIOLA IBARRA</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3489.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>74804.00999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>65824.42</v>
       </c>
       <c r="M6" t="n">
-        <v>74804.00999999999</v>
+        <v>65824.42</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>120596</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -625,38 +625,134 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>OLGA SOFIA GAXIOLA IBARRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2423.81</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2423.81</v>
       </c>
       <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>120890.51</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26661.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>147552.42</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>116795</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1603.03</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1603.03</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>120704</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRUNO PADILLA SALDATE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>76268.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>36164.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>112433.1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
+      <c r="K9" t="n">
+        <v>43536.36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>43536.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>87072.72</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
